--- a/Employee_Reports_wi52/Kasansula Francis Kiwanuka Q0527.xlsx
+++ b/Employee_Reports_wi52/Kasansula Francis Kiwanuka Q0527.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-163</v>
+        <v>-171</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-160</v>
+        <v>-168</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-148</v>
+        <v>-156</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
